--- a/루페이 정리.xlsx
+++ b/루페이 정리.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\39 루페이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498C197E-1071-4A6E-BAB1-5850B35C2393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69A569D-5DAB-47D6-8919-0C4F2E6C632F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="845" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7965" yWindow="75" windowWidth="24015" windowHeight="15090" tabRatio="845" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="223">
   <si>
     <t>레벨 예약 단계 수량</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -94,22 +94,6 @@
   </si>
   <si>
     <t>각 레벨별 최소, 최대 예약수량임</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>브론즈바</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>실버바</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>골드바</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>브론즈바의 예약수량 기준이 만족되면 실버바의 예약가능수량이 생기고, 실버바의 기준이 생기면 골드바의 예약가능 수량이 생긴다</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -183,14 +167,6 @@
   <si>
     <t>판매자의
 의무</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>본인 레벨, 현재 포인트, 브론즈바,실버바,골드바의 예약가능 수량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>각 바의 단계별 보유수량</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1320,6 +1296,18 @@
   </si>
   <si>
     <t>가 8개 , 나 2개, 다 4개 총 14개 매칭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수정의 예약수량 기준이 만족되면 루비의 예약가능수량이 생기고, 루비의 기준이 생기면 다이아의 예약가능 수량이 생긴다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>본인 레벨, 현재 포인트, 수정,루비,다이아의 예약가능 수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>각 아이템의 단계별 보유수량</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3238,6 +3226,9 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="23" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3247,6 +3238,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3256,9 +3253,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3271,12 +3265,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -3313,35 +3301,62 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="36" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="36" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3388,36 +3403,66 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3440,63 +3485,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3808,82 +3796,82 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -3909,117 +3897,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A1" s="188" t="s">
+      <c r="A1" s="182" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="188"/>
-      <c r="C1" s="188"/>
-      <c r="D1" s="188"/>
-      <c r="E1" s="188"/>
-      <c r="F1" s="188"/>
-      <c r="G1" s="188"/>
-      <c r="H1" s="188"/>
-      <c r="I1" s="188"/>
-      <c r="J1" s="188"/>
-      <c r="K1" s="188"/>
-      <c r="L1" s="188"/>
-      <c r="M1" s="188"/>
-      <c r="N1" s="188"/>
-      <c r="O1" s="188"/>
-      <c r="P1" s="188"/>
-      <c r="Q1" s="188"/>
-      <c r="R1" s="188"/>
-      <c r="S1" s="188"/>
-      <c r="T1" s="188"/>
-      <c r="U1" s="188"/>
-      <c r="V1" s="188"/>
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="182"/>
+      <c r="F1" s="182"/>
+      <c r="G1" s="182"/>
+      <c r="H1" s="182"/>
+      <c r="I1" s="182"/>
+      <c r="J1" s="182"/>
+      <c r="K1" s="182"/>
+      <c r="L1" s="182"/>
+      <c r="M1" s="182"/>
+      <c r="N1" s="182"/>
+      <c r="O1" s="182"/>
+      <c r="P1" s="182"/>
+      <c r="Q1" s="182"/>
+      <c r="R1" s="182"/>
+      <c r="S1" s="182"/>
+      <c r="T1" s="182"/>
+      <c r="U1" s="182"/>
+      <c r="V1" s="182"/>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" s="188"/>
-      <c r="B2" s="188"/>
-      <c r="C2" s="188"/>
-      <c r="D2" s="188"/>
-      <c r="E2" s="188"/>
-      <c r="F2" s="188"/>
-      <c r="G2" s="188"/>
-      <c r="H2" s="188"/>
-      <c r="I2" s="188"/>
-      <c r="J2" s="188"/>
-      <c r="K2" s="188"/>
-      <c r="L2" s="188"/>
-      <c r="M2" s="188"/>
-      <c r="N2" s="188"/>
-      <c r="O2" s="188"/>
-      <c r="P2" s="188"/>
-      <c r="Q2" s="188"/>
-      <c r="R2" s="188"/>
-      <c r="S2" s="188"/>
-      <c r="T2" s="188"/>
-      <c r="U2" s="188"/>
-      <c r="V2" s="188"/>
+      <c r="A2" s="182"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="182"/>
+      <c r="G2" s="182"/>
+      <c r="H2" s="182"/>
+      <c r="I2" s="182"/>
+      <c r="J2" s="182"/>
+      <c r="K2" s="182"/>
+      <c r="L2" s="182"/>
+      <c r="M2" s="182"/>
+      <c r="N2" s="182"/>
+      <c r="O2" s="182"/>
+      <c r="P2" s="182"/>
+      <c r="Q2" s="182"/>
+      <c r="R2" s="182"/>
+      <c r="S2" s="182"/>
+      <c r="T2" s="182"/>
+      <c r="U2" s="182"/>
+      <c r="V2" s="182"/>
     </row>
     <row r="3" spans="1:31" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="188"/>
-      <c r="B3" s="188"/>
+      <c r="A3" s="182"/>
+      <c r="B3" s="182"/>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A4" s="182" t="s">
+      <c r="A4" s="183" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="184"/>
-      <c r="C4" s="182" t="s">
+      <c r="B4" s="185"/>
+      <c r="C4" s="183" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="184"/>
-      <c r="E4" s="185" t="s">
+      <c r="D4" s="185"/>
+      <c r="E4" s="188" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="186"/>
-      <c r="G4" s="187"/>
-      <c r="H4" s="182" t="s">
+      <c r="F4" s="189"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="183" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="183"/>
-      <c r="J4" s="184"/>
-      <c r="K4" s="182" t="s">
+      <c r="I4" s="184"/>
+      <c r="J4" s="185"/>
+      <c r="K4" s="183" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="183"/>
-      <c r="M4" s="184"/>
-      <c r="N4" s="182" t="s">
+      <c r="L4" s="184"/>
+      <c r="M4" s="185"/>
+      <c r="N4" s="183" t="s">
         <v>6</v>
       </c>
-      <c r="O4" s="183"/>
-      <c r="P4" s="184"/>
-      <c r="Q4" s="182" t="s">
+      <c r="O4" s="184"/>
+      <c r="P4" s="185"/>
+      <c r="Q4" s="183" t="s">
         <v>7</v>
       </c>
-      <c r="R4" s="183"/>
-      <c r="S4" s="184"/>
-      <c r="T4" s="182" t="s">
+      <c r="R4" s="184"/>
+      <c r="S4" s="185"/>
+      <c r="T4" s="183" t="s">
         <v>8</v>
       </c>
-      <c r="U4" s="183"/>
-      <c r="V4" s="184"/>
-      <c r="W4" s="182" t="s">
+      <c r="U4" s="184"/>
+      <c r="V4" s="185"/>
+      <c r="W4" s="183" t="s">
         <v>11</v>
       </c>
-      <c r="X4" s="183"/>
-      <c r="Y4" s="184"/>
-      <c r="Z4" s="182" t="s">
+      <c r="X4" s="184"/>
+      <c r="Y4" s="185"/>
+      <c r="Z4" s="183" t="s">
         <v>12</v>
       </c>
-      <c r="AA4" s="183"/>
-      <c r="AB4" s="184"/>
-      <c r="AC4" s="185" t="s">
+      <c r="AA4" s="184"/>
+      <c r="AB4" s="185"/>
+      <c r="AC4" s="188" t="s">
         <v>13</v>
       </c>
-      <c r="AD4" s="186"/>
-      <c r="AE4" s="187"/>
+      <c r="AD4" s="189"/>
+      <c r="AE4" s="190"/>
     </row>
     <row r="5" spans="1:31" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="193"/>
-      <c r="B5" s="194"/>
+      <c r="A5" s="186"/>
+      <c r="B5" s="187"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -4091,10 +4079,10 @@
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A6" s="189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="190"/>
+      <c r="A6" s="191" t="s">
+        <v>163</v>
+      </c>
+      <c r="B6" s="192"/>
       <c r="C6" s="4">
         <v>1</v>
       </c>
@@ -4184,10 +4172,10 @@
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A7" s="191" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="192"/>
+      <c r="A7" s="193" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="194"/>
       <c r="C7" s="7"/>
       <c r="D7" s="8">
         <v>1</v>
@@ -4275,10 +4263,10 @@
       </c>
     </row>
     <row r="8" spans="1:31" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="193" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="194"/>
+      <c r="A8" s="186" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="187"/>
       <c r="C8" s="10"/>
       <c r="D8" s="11">
         <v>1</v>
@@ -4372,60 +4360,60 @@
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A13" s="188" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="188"/>
-      <c r="C13" s="188"/>
-      <c r="D13" s="188"/>
-      <c r="E13" s="188"/>
-      <c r="F13" s="188"/>
-      <c r="G13" s="188"/>
-      <c r="H13" s="188"/>
-      <c r="I13" s="188"/>
+      <c r="A13" s="182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="182"/>
+      <c r="C13" s="182"/>
+      <c r="D13" s="182"/>
+      <c r="E13" s="182"/>
+      <c r="F13" s="182"/>
+      <c r="G13" s="182"/>
+      <c r="H13" s="182"/>
+      <c r="I13" s="182"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A14" s="188"/>
-      <c r="B14" s="188"/>
-      <c r="C14" s="188"/>
-      <c r="D14" s="188"/>
-      <c r="E14" s="188"/>
-      <c r="F14" s="188"/>
-      <c r="G14" s="188"/>
-      <c r="H14" s="188"/>
-      <c r="I14" s="188"/>
+      <c r="A14" s="182"/>
+      <c r="B14" s="182"/>
+      <c r="C14" s="182"/>
+      <c r="D14" s="182"/>
+      <c r="E14" s="182"/>
+      <c r="F14" s="182"/>
+      <c r="G14" s="182"/>
+      <c r="H14" s="182"/>
+      <c r="I14" s="182"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="F16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="G16" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="H16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="I16" s="13" t="s">
         <v>24</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -4459,106 +4447,106 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="188" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="188"/>
-      <c r="C24" s="188"/>
-      <c r="D24" s="188"/>
-      <c r="E24" s="188"/>
-      <c r="F24" s="188"/>
-      <c r="G24" s="188"/>
-      <c r="H24" s="188"/>
-      <c r="I24" s="188"/>
-      <c r="J24" s="188"/>
-      <c r="K24" s="188"/>
-      <c r="L24" s="188"/>
-      <c r="M24" s="188"/>
-      <c r="N24" s="188"/>
+      <c r="A24" s="182" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="182"/>
+      <c r="C24" s="182"/>
+      <c r="D24" s="182"/>
+      <c r="E24" s="182"/>
+      <c r="F24" s="182"/>
+      <c r="G24" s="182"/>
+      <c r="H24" s="182"/>
+      <c r="I24" s="182"/>
+      <c r="J24" s="182"/>
+      <c r="K24" s="182"/>
+      <c r="L24" s="182"/>
+      <c r="M24" s="182"/>
+      <c r="N24" s="182"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="188"/>
-      <c r="B25" s="188"/>
-      <c r="C25" s="188"/>
-      <c r="D25" s="188"/>
-      <c r="E25" s="188"/>
-      <c r="F25" s="188"/>
-      <c r="G25" s="188"/>
-      <c r="H25" s="188"/>
-      <c r="I25" s="188"/>
-      <c r="J25" s="188"/>
-      <c r="K25" s="188"/>
-      <c r="L25" s="188"/>
-      <c r="M25" s="188"/>
-      <c r="N25" s="188"/>
+      <c r="A25" s="182"/>
+      <c r="B25" s="182"/>
+      <c r="C25" s="182"/>
+      <c r="D25" s="182"/>
+      <c r="E25" s="182"/>
+      <c r="F25" s="182"/>
+      <c r="G25" s="182"/>
+      <c r="H25" s="182"/>
+      <c r="I25" s="182"/>
+      <c r="J25" s="182"/>
+      <c r="K25" s="182"/>
+      <c r="L25" s="182"/>
+      <c r="M25" s="182"/>
+      <c r="N25" s="182"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="188"/>
-      <c r="B26" s="188"/>
-      <c r="C26" s="188"/>
-      <c r="D26" s="188"/>
-      <c r="E26" s="188"/>
-      <c r="F26" s="188"/>
-      <c r="G26" s="188"/>
-      <c r="H26" s="188"/>
-      <c r="I26" s="188"/>
-      <c r="J26" s="188"/>
-      <c r="K26" s="188"/>
-      <c r="L26" s="188"/>
-      <c r="M26" s="188"/>
-      <c r="N26" s="188"/>
+      <c r="A26" s="182"/>
+      <c r="B26" s="182"/>
+      <c r="C26" s="182"/>
+      <c r="D26" s="182"/>
+      <c r="E26" s="182"/>
+      <c r="F26" s="182"/>
+      <c r="G26" s="182"/>
+      <c r="H26" s="182"/>
+      <c r="I26" s="182"/>
+      <c r="J26" s="182"/>
+      <c r="K26" s="182"/>
+      <c r="L26" s="182"/>
+      <c r="M26" s="182"/>
+      <c r="N26" s="182"/>
     </row>
     <row r="27" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="1:14" ht="27.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="26" t="s">
-        <v>15</v>
+        <v>163</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>16</v>
+        <v>164</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I28" s="19" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K28" s="26" t="s">
-        <v>17</v>
+        <v>165</v>
       </c>
       <c r="L28" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="M28" s="18" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="N28" s="19" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5344,66 +5332,74 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>39</v>
+        <v>221</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>40</v>
+        <v>222</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="Z4:AB4"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="W4:Y4"/>
+    <mergeCell ref="A13:I14"/>
+    <mergeCell ref="A24:N26"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A1:V2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="N4:P4"/>
@@ -5414,14 +5410,6 @@
     <mergeCell ref="K4:M4"/>
     <mergeCell ref="Q4:S4"/>
     <mergeCell ref="T4:V4"/>
-    <mergeCell ref="Z4:AB4"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="W4:Y4"/>
-    <mergeCell ref="A13:I14"/>
-    <mergeCell ref="A24:N26"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5443,36 +5431,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B1" s="188" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="188"/>
-      <c r="D1" s="188"/>
-      <c r="E1" s="188"/>
-      <c r="F1" s="188"/>
-      <c r="G1" s="188"/>
+      <c r="B1" s="182" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="182"/>
+      <c r="F1" s="182"/>
+      <c r="G1" s="182"/>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="188"/>
-      <c r="C2" s="188"/>
-      <c r="D2" s="188"/>
-      <c r="E2" s="188"/>
-      <c r="F2" s="188"/>
-      <c r="G2" s="188"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="182"/>
+      <c r="G2" s="182"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="188"/>
-      <c r="C3" s="188"/>
-      <c r="D3" s="188"/>
-      <c r="E3" s="188"/>
-      <c r="F3" s="188"/>
-      <c r="G3" s="188"/>
+      <c r="B3" s="182"/>
+      <c r="C3" s="182"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="182"/>
+      <c r="F3" s="182"/>
+      <c r="G3" s="182"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="27"/>
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E4" s="27"/>
       <c r="F4" s="27"/>
@@ -5480,86 +5468,86 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="188" t="s">
-        <v>78</v>
+        <v>58</v>
+      </c>
+      <c r="C5" s="182" t="s">
+        <v>72</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="27"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="182"/>
+      <c r="D6" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="188"/>
-      <c r="D6" s="27" t="s">
-        <v>66</v>
-      </c>
       <c r="E6" s="28" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F6" s="27"/>
       <c r="G6" s="27"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="188"/>
+        <v>55</v>
+      </c>
+      <c r="C7" s="182"/>
       <c r="D7" s="27" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F7" s="27"/>
       <c r="G7" s="27"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="188"/>
+        <v>66</v>
+      </c>
+      <c r="C8" s="182"/>
       <c r="D8" s="29" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F8" s="29"/>
       <c r="G8" s="29"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="188"/>
+        <v>65</v>
+      </c>
+      <c r="C9" s="182"/>
       <c r="D9" s="27" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F9" s="27"/>
       <c r="G9" s="27"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="188"/>
+        <v>68</v>
+      </c>
+      <c r="C10" s="182"/>
       <c r="D10" s="27" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F10" s="27"/>
       <c r="G10" s="27"/>
@@ -5606,15 +5594,15 @@
     </row>
     <row r="16" spans="2:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C16" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="195" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C17" s="197" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D17" s="197"/>
       <c r="E17" s="197"/>
@@ -5736,10 +5724,10 @@
     </row>
     <row r="32" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="195" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C32" s="198" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D32" s="198"/>
       <c r="E32" s="198"/>
@@ -5878,54 +5866,54 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B1" s="188" t="s">
-        <v>90</v>
-      </c>
-      <c r="C1" s="188"/>
-      <c r="D1" s="188"/>
-      <c r="E1" s="188"/>
-      <c r="F1" s="188"/>
-      <c r="G1" s="188"/>
-      <c r="H1" s="188"/>
-      <c r="I1" s="188"/>
-      <c r="J1" s="188"/>
-      <c r="K1" s="188"/>
-      <c r="L1" s="188"/>
-      <c r="M1" s="188"/>
-      <c r="N1" s="188"/>
-      <c r="O1" s="188"/>
+      <c r="B1" s="182" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="182"/>
+      <c r="F1" s="182"/>
+      <c r="G1" s="182"/>
+      <c r="H1" s="182"/>
+      <c r="I1" s="182"/>
+      <c r="J1" s="182"/>
+      <c r="K1" s="182"/>
+      <c r="L1" s="182"/>
+      <c r="M1" s="182"/>
+      <c r="N1" s="182"/>
+      <c r="O1" s="182"/>
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="188"/>
-      <c r="C2" s="188"/>
-      <c r="D2" s="188"/>
-      <c r="E2" s="188"/>
-      <c r="F2" s="188"/>
-      <c r="G2" s="188"/>
-      <c r="H2" s="188"/>
-      <c r="I2" s="188"/>
-      <c r="J2" s="188"/>
-      <c r="K2" s="188"/>
-      <c r="L2" s="188"/>
-      <c r="M2" s="188"/>
-      <c r="N2" s="188"/>
-      <c r="O2" s="188"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="182"/>
+      <c r="G2" s="182"/>
+      <c r="H2" s="182"/>
+      <c r="I2" s="182"/>
+      <c r="J2" s="182"/>
+      <c r="K2" s="182"/>
+      <c r="L2" s="182"/>
+      <c r="M2" s="182"/>
+      <c r="N2" s="182"/>
+      <c r="O2" s="182"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="188"/>
-      <c r="C3" s="188"/>
-      <c r="D3" s="188"/>
-      <c r="E3" s="188"/>
-      <c r="F3" s="188"/>
-      <c r="G3" s="188"/>
-      <c r="H3" s="188"/>
-      <c r="I3" s="188"/>
-      <c r="J3" s="188"/>
-      <c r="K3" s="188"/>
-      <c r="L3" s="188"/>
-      <c r="M3" s="188"/>
-      <c r="N3" s="188"/>
-      <c r="O3" s="188"/>
+      <c r="B3" s="182"/>
+      <c r="C3" s="182"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="182"/>
+      <c r="F3" s="182"/>
+      <c r="G3" s="182"/>
+      <c r="H3" s="182"/>
+      <c r="I3" s="182"/>
+      <c r="J3" s="182"/>
+      <c r="K3" s="182"/>
+      <c r="L3" s="182"/>
+      <c r="M3" s="182"/>
+      <c r="N3" s="182"/>
+      <c r="O3" s="182"/>
     </row>
     <row r="5" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -6033,40 +6021,40 @@
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="200" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G12" s="200" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="L12" s="200" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M12" s="13" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.3">
@@ -6106,31 +6094,31 @@
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B15" s="201" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G15" s="201" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="L15" s="201" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="M15" s="13" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.3">
@@ -6206,19 +6194,19 @@
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" s="199" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C20" s="199"/>
       <c r="D20" s="199"/>
       <c r="E20" s="199"/>
       <c r="G20" s="199" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H20" s="199"/>
       <c r="I20" s="199"/>
       <c r="J20" s="199"/>
       <c r="L20" s="199" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="M20" s="199"/>
       <c r="N20" s="199"/>
@@ -6323,13 +6311,13 @@
     <row r="2" spans="2:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="2:4" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="32" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C3" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="33" t="s">
         <v>92</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6337,7 +6325,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D4" s="35">
         <v>1000</v>
@@ -6348,7 +6336,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D5" s="37">
         <v>3000</v>
@@ -6359,7 +6347,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D6" s="38">
         <v>6000</v>
@@ -6370,7 +6358,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D7" s="39">
         <v>15000</v>
@@ -6381,7 +6369,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D8" s="35">
         <v>30000</v>
@@ -6389,7 +6377,7 @@
     </row>
     <row r="9" spans="2:4" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="202" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C9" s="203"/>
       <c r="D9" s="204"/>
@@ -6432,150 +6420,150 @@
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="200" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C4" s="41" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D4" s="41" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E4" s="41" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G4" s="46" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="200"/>
       <c r="B5" s="41" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C5" s="13">
         <v>150</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E5" s="42" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="200"/>
       <c r="B6" s="41" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C6" s="13">
         <v>450</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E6" s="42" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="200"/>
       <c r="B7" s="41" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C7" s="13">
         <v>960</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E7" s="42" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="200"/>
       <c r="B8" s="41" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C8" s="13">
         <v>1740</v>
       </c>
       <c r="D8" s="41" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="200"/>
       <c r="B9" s="41" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C9" s="13">
         <v>2850</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="200"/>
       <c r="B10" s="41" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C10" s="13">
         <v>4350</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="200"/>
       <c r="B11" s="41" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C11" s="13">
         <v>6450</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E11" s="42" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="200"/>
       <c r="B12" s="43" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C12" s="44">
         <v>9450</v>
       </c>
       <c r="D12" s="43" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F12" s="205"/>
       <c r="G12" s="206"/>
@@ -6588,16 +6576,16 @@
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="200"/>
       <c r="B13" s="43" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C13" s="44">
         <v>12450</v>
       </c>
       <c r="D13" s="43" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F13" s="205"/>
       <c r="G13" s="206"/>
@@ -6610,7 +6598,7 @@
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="200"/>
       <c r="B14" s="43" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C14" s="44"/>
       <c r="D14" s="44"/>
@@ -6625,33 +6613,33 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="200" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B17" s="200"/>
       <c r="C17" s="200" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D17" s="200"/>
       <c r="E17" s="42" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="200"/>
       <c r="B18" s="200"/>
       <c r="C18" s="200" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D18" s="200"/>
       <c r="E18" s="42" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="200"/>
       <c r="B19" s="200"/>
       <c r="C19" s="201" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D19" s="201"/>
       <c r="E19" s="201"/>
@@ -6686,11 +6674,11 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="201" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B25" s="200"/>
       <c r="C25" s="201" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D25" s="201"/>
       <c r="E25" s="201"/>
@@ -6718,11 +6706,11 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="201" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B29" s="200"/>
       <c r="C29" s="201" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D29" s="201"/>
       <c r="E29" s="201"/>
@@ -6750,16 +6738,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A25:B28"/>
+    <mergeCell ref="C25:E28"/>
+    <mergeCell ref="A29:B32"/>
+    <mergeCell ref="C29:E32"/>
+    <mergeCell ref="A4:A14"/>
     <mergeCell ref="F12:L14"/>
     <mergeCell ref="A17:B23"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:E23"/>
-    <mergeCell ref="A25:B28"/>
-    <mergeCell ref="C25:E28"/>
-    <mergeCell ref="A29:B32"/>
-    <mergeCell ref="C29:E32"/>
-    <mergeCell ref="A4:A14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6777,28 +6765,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="208" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="208"/>
-      <c r="C1" s="208"/>
-      <c r="D1" s="208"/>
+      <c r="A1" s="207" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
       <c r="E1" s="49"/>
       <c r="F1" s="50"/>
       <c r="G1" s="50"/>
-      <c r="H1" s="209" t="s">
-        <v>132</v>
-      </c>
-      <c r="I1" s="209"/>
-      <c r="J1" s="209"/>
-      <c r="K1" s="209"/>
+      <c r="H1" s="216" t="s">
+        <v>126</v>
+      </c>
+      <c r="I1" s="216"/>
+      <c r="J1" s="216"/>
+      <c r="K1" s="216"/>
       <c r="L1" s="50"/>
       <c r="M1" s="49"/>
       <c r="N1" s="49"/>
     </row>
     <row r="2" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="49" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B2" s="50">
         <v>100</v>
@@ -6813,39 +6801,39 @@
       <c r="E2" s="49"/>
       <c r="F2" s="50"/>
       <c r="G2" s="50"/>
-      <c r="H2" s="209"/>
-      <c r="I2" s="209"/>
-      <c r="J2" s="209"/>
-      <c r="K2" s="209"/>
+      <c r="H2" s="216"/>
+      <c r="I2" s="216"/>
+      <c r="J2" s="216"/>
+      <c r="K2" s="216"/>
       <c r="L2" s="50"/>
       <c r="M2" s="49"/>
       <c r="N2" s="49"/>
     </row>
     <row r="3" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="51" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B3" s="52" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C3" s="52" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D3" s="53" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E3" s="49"/>
       <c r="F3" s="54"/>
       <c r="G3" s="49"/>
       <c r="H3" s="55"/>
       <c r="I3" s="50" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J3" s="50" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="K3" s="50" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="L3" s="50"/>
       <c r="M3" s="50"/>
@@ -6881,7 +6869,7 @@
         <f>J4-I4</f>
         <v>8050</v>
       </c>
-      <c r="L4" s="208"/>
+      <c r="L4" s="207"/>
       <c r="M4" s="59"/>
       <c r="N4" s="59"/>
     </row>
@@ -6905,7 +6893,7 @@
       <c r="I5" s="211"/>
       <c r="J5" s="213"/>
       <c r="K5" s="211"/>
-      <c r="L5" s="208"/>
+      <c r="L5" s="207"/>
       <c r="M5" s="59"/>
       <c r="N5" s="59"/>
     </row>
@@ -6940,7 +6928,7 @@
         <f>J6-I6</f>
         <v>9750</v>
       </c>
-      <c r="L6" s="208"/>
+      <c r="L6" s="207"/>
       <c r="M6" s="59"/>
       <c r="N6" s="59"/>
     </row>
@@ -6964,7 +6952,7 @@
       <c r="I7" s="211"/>
       <c r="J7" s="213"/>
       <c r="K7" s="211"/>
-      <c r="L7" s="208"/>
+      <c r="L7" s="207"/>
       <c r="M7" s="59"/>
       <c r="N7" s="59"/>
     </row>
@@ -7042,15 +7030,15 @@
       <c r="F10" s="49"/>
       <c r="G10" s="65"/>
       <c r="H10" s="65" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I10" s="65" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="J10" s="65" t="s">
-        <v>133</v>
-      </c>
-      <c r="K10" s="207"/>
+        <v>127</v>
+      </c>
+      <c r="K10" s="214"/>
       <c r="L10" s="50"/>
       <c r="M10" s="59"/>
       <c r="N10" s="59"/>
@@ -7071,7 +7059,7 @@
       <c r="E11" s="49"/>
       <c r="F11" s="49"/>
       <c r="G11" s="65" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H11" s="66">
         <v>78000</v>
@@ -7084,7 +7072,7 @@
         <f>I11-H11</f>
         <v>17800</v>
       </c>
-      <c r="K11" s="207"/>
+      <c r="K11" s="214"/>
       <c r="L11" s="50"/>
       <c r="M11" s="59"/>
       <c r="N11" s="59"/>
@@ -7105,7 +7093,7 @@
       <c r="E12" s="49"/>
       <c r="F12" s="49"/>
       <c r="G12" s="65" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H12" s="67"/>
       <c r="I12" s="67">
@@ -7116,7 +7104,7 @@
         <f>I12-H11</f>
         <v>61900</v>
       </c>
-      <c r="K12" s="207"/>
+      <c r="K12" s="214"/>
       <c r="L12" s="50"/>
       <c r="M12" s="59"/>
       <c r="N12" s="59"/>
@@ -7161,19 +7149,19 @@
       <c r="E14" s="49"/>
       <c r="F14" s="49"/>
       <c r="G14" s="210" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H14" s="67" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I14" s="67" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="J14" s="67" t="s">
+        <v>127</v>
+      </c>
+      <c r="K14" s="214" t="s">
         <v>133</v>
-      </c>
-      <c r="K14" s="207" t="s">
-        <v>139</v>
       </c>
       <c r="L14" s="54"/>
       <c r="M14" s="50"/>
@@ -7207,7 +7195,7 @@
         <f>I15-H15</f>
         <v>61900</v>
       </c>
-      <c r="K15" s="207"/>
+      <c r="K15" s="214"/>
       <c r="L15" s="54"/>
       <c r="M15" s="59"/>
       <c r="N15" s="59"/>
@@ -7227,13 +7215,13 @@
       </c>
       <c r="E16" s="49"/>
       <c r="F16" s="49"/>
-      <c r="G16" s="215" t="s">
-        <v>140</v>
-      </c>
-      <c r="H16" s="215"/>
-      <c r="I16" s="215"/>
-      <c r="J16" s="215"/>
-      <c r="K16" s="207"/>
+      <c r="G16" s="208" t="s">
+        <v>134</v>
+      </c>
+      <c r="H16" s="208"/>
+      <c r="I16" s="208"/>
+      <c r="J16" s="208"/>
+      <c r="K16" s="214"/>
       <c r="L16" s="54"/>
       <c r="M16" s="59"/>
       <c r="N16" s="59"/>
@@ -7253,11 +7241,11 @@
       </c>
       <c r="E17" s="49"/>
       <c r="F17" s="49"/>
-      <c r="G17" s="215"/>
-      <c r="H17" s="215"/>
-      <c r="I17" s="215"/>
-      <c r="J17" s="215"/>
-      <c r="K17" s="207"/>
+      <c r="G17" s="208"/>
+      <c r="H17" s="208"/>
+      <c r="I17" s="208"/>
+      <c r="J17" s="208"/>
+      <c r="K17" s="214"/>
       <c r="L17" s="54"/>
       <c r="M17" s="59"/>
       <c r="N17" s="59"/>
@@ -7277,11 +7265,11 @@
       </c>
       <c r="E18" s="49"/>
       <c r="F18" s="49"/>
-      <c r="G18" s="215"/>
-      <c r="H18" s="215"/>
-      <c r="I18" s="215"/>
-      <c r="J18" s="215"/>
-      <c r="K18" s="207"/>
+      <c r="G18" s="208"/>
+      <c r="H18" s="208"/>
+      <c r="I18" s="208"/>
+      <c r="J18" s="208"/>
+      <c r="K18" s="214"/>
       <c r="L18" s="50"/>
       <c r="M18" s="59"/>
       <c r="N18" s="59"/>
@@ -7325,13 +7313,13 @@
       </c>
       <c r="E20" s="49"/>
       <c r="F20" s="49"/>
-      <c r="G20" s="216" t="s">
-        <v>141</v>
-      </c>
-      <c r="H20" s="216"/>
-      <c r="I20" s="216"/>
-      <c r="J20" s="216"/>
-      <c r="K20" s="216"/>
+      <c r="G20" s="209" t="s">
+        <v>135</v>
+      </c>
+      <c r="H20" s="209"/>
+      <c r="I20" s="209"/>
+      <c r="J20" s="209"/>
+      <c r="K20" s="209"/>
       <c r="L20" s="50"/>
       <c r="M20" s="59"/>
       <c r="N20" s="59"/>
@@ -7351,13 +7339,13 @@
       </c>
       <c r="E21" s="49"/>
       <c r="F21" s="49"/>
-      <c r="G21" s="216"/>
-      <c r="H21" s="216"/>
-      <c r="I21" s="216"/>
-      <c r="J21" s="216"/>
-      <c r="K21" s="216"/>
-      <c r="L21" s="208" t="s">
-        <v>142</v>
+      <c r="G21" s="209"/>
+      <c r="H21" s="209"/>
+      <c r="I21" s="209"/>
+      <c r="J21" s="209"/>
+      <c r="K21" s="209"/>
+      <c r="L21" s="207" t="s">
+        <v>136</v>
       </c>
       <c r="M21" s="59"/>
       <c r="N21" s="59"/>
@@ -7377,12 +7365,12 @@
       </c>
       <c r="E22" s="49"/>
       <c r="F22" s="49"/>
-      <c r="G22" s="216"/>
-      <c r="H22" s="216"/>
-      <c r="I22" s="216"/>
-      <c r="J22" s="216"/>
-      <c r="K22" s="216"/>
-      <c r="L22" s="208"/>
+      <c r="G22" s="209"/>
+      <c r="H22" s="209"/>
+      <c r="I22" s="209"/>
+      <c r="J22" s="209"/>
+      <c r="K22" s="209"/>
+      <c r="L22" s="207"/>
       <c r="M22" s="59"/>
       <c r="N22" s="59"/>
     </row>
@@ -7401,12 +7389,12 @@
       </c>
       <c r="E23" s="49"/>
       <c r="F23" s="49"/>
-      <c r="G23" s="216"/>
-      <c r="H23" s="216"/>
-      <c r="I23" s="216"/>
-      <c r="J23" s="216"/>
-      <c r="K23" s="216"/>
-      <c r="L23" s="208"/>
+      <c r="G23" s="209"/>
+      <c r="H23" s="209"/>
+      <c r="I23" s="209"/>
+      <c r="J23" s="209"/>
+      <c r="K23" s="209"/>
+      <c r="L23" s="207"/>
       <c r="M23" s="49"/>
       <c r="N23" s="49"/>
     </row>
@@ -7425,12 +7413,12 @@
       </c>
       <c r="E24" s="49"/>
       <c r="F24" s="49"/>
-      <c r="G24" s="216"/>
-      <c r="H24" s="216"/>
-      <c r="I24" s="216"/>
-      <c r="J24" s="216"/>
-      <c r="K24" s="216"/>
-      <c r="L24" s="208"/>
+      <c r="G24" s="209"/>
+      <c r="H24" s="209"/>
+      <c r="I24" s="209"/>
+      <c r="J24" s="209"/>
+      <c r="K24" s="209"/>
+      <c r="L24" s="207"/>
       <c r="M24" s="50"/>
       <c r="N24" s="50"/>
     </row>
@@ -7475,34 +7463,34 @@
       <c r="N26" s="59"/>
     </row>
     <row r="27" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="214" t="s">
-        <v>143</v>
-      </c>
-      <c r="B27" s="214"/>
-      <c r="C27" s="214"/>
-      <c r="D27" s="214"/>
+      <c r="A27" s="215" t="s">
+        <v>137</v>
+      </c>
+      <c r="B27" s="215"/>
+      <c r="C27" s="215"/>
+      <c r="D27" s="215"/>
       <c r="E27" s="54"/>
       <c r="F27" s="54"/>
       <c r="G27" s="49"/>
       <c r="H27" s="50"/>
       <c r="I27" s="50" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J27" s="50" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="K27" s="50" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="L27" s="78"/>
       <c r="M27" s="59"/>
       <c r="N27" s="59"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="214"/>
-      <c r="B28" s="214"/>
-      <c r="C28" s="214"/>
-      <c r="D28" s="214"/>
+      <c r="A28" s="215"/>
+      <c r="B28" s="215"/>
+      <c r="C28" s="215"/>
+      <c r="D28" s="215"/>
       <c r="E28" s="54"/>
       <c r="F28" s="54"/>
       <c r="G28" s="49"/>
@@ -7526,10 +7514,10 @@
       <c r="N28" s="59"/>
     </row>
     <row r="29" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="214"/>
-      <c r="B29" s="214"/>
-      <c r="C29" s="214"/>
-      <c r="D29" s="214"/>
+      <c r="A29" s="215"/>
+      <c r="B29" s="215"/>
+      <c r="C29" s="215"/>
+      <c r="D29" s="215"/>
       <c r="E29" s="54"/>
       <c r="F29" s="54"/>
       <c r="G29" s="49"/>
@@ -7542,10 +7530,10 @@
       <c r="N29" s="59"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="214"/>
-      <c r="B30" s="214"/>
-      <c r="C30" s="214"/>
-      <c r="D30" s="214"/>
+      <c r="A30" s="215"/>
+      <c r="B30" s="215"/>
+      <c r="C30" s="215"/>
+      <c r="D30" s="215"/>
       <c r="E30" s="54"/>
       <c r="F30" s="54"/>
       <c r="G30" s="49"/>
@@ -7569,10 +7557,10 @@
       <c r="N30" s="59"/>
     </row>
     <row r="31" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="214"/>
-      <c r="B31" s="214"/>
-      <c r="C31" s="214"/>
-      <c r="D31" s="214"/>
+      <c r="A31" s="215"/>
+      <c r="B31" s="215"/>
+      <c r="C31" s="215"/>
+      <c r="D31" s="215"/>
       <c r="E31" s="54"/>
       <c r="F31" s="54"/>
       <c r="G31" s="49"/>
@@ -7585,10 +7573,10 @@
       <c r="N31" s="59"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="214"/>
-      <c r="B32" s="214"/>
-      <c r="C32" s="214"/>
-      <c r="D32" s="214"/>
+      <c r="A32" s="215"/>
+      <c r="B32" s="215"/>
+      <c r="C32" s="215"/>
+      <c r="D32" s="215"/>
       <c r="E32" s="54"/>
       <c r="F32" s="54"/>
       <c r="G32" s="49"/>
@@ -7610,10 +7598,10 @@
       <c r="N32" s="59"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="214"/>
-      <c r="B33" s="214"/>
-      <c r="C33" s="214"/>
-      <c r="D33" s="214"/>
+      <c r="A33" s="215"/>
+      <c r="B33" s="215"/>
+      <c r="C33" s="215"/>
+      <c r="D33" s="215"/>
       <c r="E33" s="54"/>
       <c r="F33" s="54"/>
       <c r="G33" s="49"/>
@@ -7626,36 +7614,36 @@
       <c r="N33" s="49"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="214"/>
-      <c r="B34" s="214"/>
-      <c r="C34" s="214"/>
-      <c r="D34" s="214"/>
+      <c r="A34" s="215"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="215"/>
+      <c r="D34" s="215"/>
       <c r="E34" s="54"/>
       <c r="F34" s="54"/>
       <c r="G34" s="65"/>
       <c r="H34" s="65" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I34" s="65" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="J34" s="65" t="s">
-        <v>133</v>
-      </c>
-      <c r="K34" s="207"/>
+        <v>127</v>
+      </c>
+      <c r="K34" s="214"/>
       <c r="L34" s="78"/>
       <c r="M34" s="49"/>
       <c r="N34" s="49"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="214"/>
-      <c r="B35" s="214"/>
-      <c r="C35" s="214"/>
-      <c r="D35" s="214"/>
+      <c r="A35" s="215"/>
+      <c r="B35" s="215"/>
+      <c r="C35" s="215"/>
+      <c r="D35" s="215"/>
       <c r="E35" s="54"/>
       <c r="F35" s="54"/>
       <c r="G35" s="65" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H35" s="66">
         <f>I32</f>
@@ -7669,20 +7657,20 @@
         <f>I35-H35</f>
         <v>16750</v>
       </c>
-      <c r="K35" s="207"/>
+      <c r="K35" s="214"/>
       <c r="L35" s="78"/>
       <c r="M35" s="49"/>
       <c r="N35" s="49"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="214"/>
-      <c r="B36" s="214"/>
-      <c r="C36" s="214"/>
-      <c r="D36" s="214"/>
+      <c r="A36" s="215"/>
+      <c r="B36" s="215"/>
+      <c r="C36" s="215"/>
+      <c r="D36" s="215"/>
       <c r="E36" s="54"/>
       <c r="F36" s="54"/>
       <c r="G36" s="65" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H36" s="67"/>
       <c r="I36" s="67">
@@ -7692,16 +7680,16 @@
         <f>I36-H35</f>
         <v>54950</v>
       </c>
-      <c r="K36" s="207"/>
+      <c r="K36" s="214"/>
       <c r="L36" s="78"/>
       <c r="M36" s="83"/>
       <c r="N36" s="49"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="214"/>
-      <c r="B37" s="214"/>
-      <c r="C37" s="214"/>
-      <c r="D37" s="214"/>
+      <c r="A37" s="215"/>
+      <c r="B37" s="215"/>
+      <c r="C37" s="215"/>
+      <c r="D37" s="215"/>
       <c r="E37" s="54"/>
       <c r="F37" s="54"/>
       <c r="G37" s="49"/>
@@ -7721,21 +7709,21 @@
       <c r="E38" s="54"/>
       <c r="F38" s="54"/>
       <c r="G38" s="210" t="s">
+        <v>132</v>
+      </c>
+      <c r="H38" s="67" t="s">
+        <v>82</v>
+      </c>
+      <c r="I38" s="67" t="s">
+        <v>81</v>
+      </c>
+      <c r="J38" s="67" t="s">
+        <v>127</v>
+      </c>
+      <c r="K38" s="214" t="s">
         <v>138</v>
       </c>
-      <c r="H38" s="67" t="s">
-        <v>88</v>
-      </c>
-      <c r="I38" s="67" t="s">
-        <v>87</v>
-      </c>
-      <c r="J38" s="67" t="s">
-        <v>133</v>
-      </c>
-      <c r="K38" s="207" t="s">
-        <v>144</v>
-      </c>
-      <c r="L38" s="208"/>
+      <c r="L38" s="207"/>
       <c r="M38" s="49"/>
       <c r="N38" s="49"/>
     </row>
@@ -7759,8 +7747,8 @@
         <f>I39-H39</f>
         <v>54950</v>
       </c>
-      <c r="K39" s="207"/>
-      <c r="L39" s="208"/>
+      <c r="K39" s="214"/>
+      <c r="L39" s="207"/>
     </row>
     <row r="40" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="54"/>
@@ -7769,14 +7757,14 @@
       <c r="D40" s="54"/>
       <c r="E40" s="54"/>
       <c r="F40" s="54"/>
-      <c r="G40" s="215" t="s">
-        <v>145</v>
-      </c>
-      <c r="H40" s="215"/>
-      <c r="I40" s="215"/>
-      <c r="J40" s="215"/>
-      <c r="K40" s="207"/>
-      <c r="L40" s="208"/>
+      <c r="G40" s="208" t="s">
+        <v>139</v>
+      </c>
+      <c r="H40" s="208"/>
+      <c r="I40" s="208"/>
+      <c r="J40" s="208"/>
+      <c r="K40" s="214"/>
+      <c r="L40" s="207"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="54"/>
@@ -7785,12 +7773,12 @@
       <c r="D41" s="54"/>
       <c r="E41" s="54"/>
       <c r="F41" s="54"/>
-      <c r="G41" s="215"/>
-      <c r="H41" s="215"/>
-      <c r="I41" s="215"/>
-      <c r="J41" s="215"/>
-      <c r="K41" s="207"/>
-      <c r="L41" s="208"/>
+      <c r="G41" s="208"/>
+      <c r="H41" s="208"/>
+      <c r="I41" s="208"/>
+      <c r="J41" s="208"/>
+      <c r="K41" s="214"/>
+      <c r="L41" s="207"/>
     </row>
     <row r="42" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="54"/>
@@ -7799,11 +7787,11 @@
       <c r="D42" s="54"/>
       <c r="E42" s="54"/>
       <c r="F42" s="54"/>
-      <c r="G42" s="215"/>
-      <c r="H42" s="215"/>
-      <c r="I42" s="215"/>
-      <c r="J42" s="215"/>
-      <c r="K42" s="207"/>
+      <c r="G42" s="208"/>
+      <c r="H42" s="208"/>
+      <c r="I42" s="208"/>
+      <c r="J42" s="208"/>
+      <c r="K42" s="214"/>
       <c r="L42" s="50"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
@@ -7827,13 +7815,13 @@
       <c r="D44" s="54"/>
       <c r="E44" s="54"/>
       <c r="F44" s="54"/>
-      <c r="G44" s="216" t="s">
-        <v>146</v>
-      </c>
-      <c r="H44" s="216"/>
-      <c r="I44" s="216"/>
-      <c r="J44" s="216"/>
-      <c r="K44" s="216"/>
+      <c r="G44" s="209" t="s">
+        <v>140</v>
+      </c>
+      <c r="H44" s="209"/>
+      <c r="I44" s="209"/>
+      <c r="J44" s="209"/>
+      <c r="K44" s="209"/>
       <c r="L44" s="78"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
@@ -7843,11 +7831,11 @@
       <c r="D45" s="54"/>
       <c r="E45" s="54"/>
       <c r="F45" s="54"/>
-      <c r="G45" s="216"/>
-      <c r="H45" s="216"/>
-      <c r="I45" s="216"/>
-      <c r="J45" s="216"/>
-      <c r="K45" s="216"/>
+      <c r="G45" s="209"/>
+      <c r="H45" s="209"/>
+      <c r="I45" s="209"/>
+      <c r="J45" s="209"/>
+      <c r="K45" s="209"/>
       <c r="L45" s="50"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
@@ -7857,11 +7845,11 @@
       <c r="D46" s="54"/>
       <c r="E46" s="54"/>
       <c r="F46" s="54"/>
-      <c r="G46" s="216"/>
-      <c r="H46" s="216"/>
-      <c r="I46" s="216"/>
-      <c r="J46" s="216"/>
-      <c r="K46" s="216"/>
+      <c r="G46" s="209"/>
+      <c r="H46" s="209"/>
+      <c r="I46" s="209"/>
+      <c r="J46" s="209"/>
+      <c r="K46" s="209"/>
       <c r="L46" s="50"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
@@ -7871,11 +7859,11 @@
       <c r="D47" s="49"/>
       <c r="E47" s="49"/>
       <c r="F47" s="49"/>
-      <c r="G47" s="216"/>
-      <c r="H47" s="216"/>
-      <c r="I47" s="216"/>
-      <c r="J47" s="216"/>
-      <c r="K47" s="216"/>
+      <c r="G47" s="209"/>
+      <c r="H47" s="209"/>
+      <c r="I47" s="209"/>
+      <c r="J47" s="209"/>
+      <c r="K47" s="209"/>
       <c r="L47" s="50"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
@@ -7885,11 +7873,11 @@
       <c r="D48" s="49"/>
       <c r="E48" s="49"/>
       <c r="F48" s="49"/>
-      <c r="G48" s="216"/>
-      <c r="H48" s="216"/>
-      <c r="I48" s="216"/>
-      <c r="J48" s="216"/>
-      <c r="K48" s="216"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="209"/>
+      <c r="K48" s="209"/>
       <c r="L48" s="50"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
@@ -7915,16 +7903,38 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:K2"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="A27:D37"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="K28:K29"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="K14:K18"/>
+    <mergeCell ref="G16:J18"/>
+    <mergeCell ref="G20:K24"/>
+    <mergeCell ref="L21:L24"/>
     <mergeCell ref="L38:L41"/>
     <mergeCell ref="G40:J42"/>
     <mergeCell ref="G44:K48"/>
@@ -7935,28 +7945,6 @@
     <mergeCell ref="K34:K36"/>
     <mergeCell ref="G38:G39"/>
     <mergeCell ref="K38:K42"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="K14:K18"/>
-    <mergeCell ref="G16:J18"/>
-    <mergeCell ref="G20:K24"/>
-    <mergeCell ref="L21:L24"/>
-    <mergeCell ref="A27:D37"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="K28:K29"/>
-    <mergeCell ref="L4:L7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="K10:K12"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:K2"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7985,26 +7973,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="221" t="s">
-        <v>160</v>
-      </c>
-      <c r="B1" s="222"/>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
-      <c r="F1" s="222"/>
+      <c r="A1" s="230" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="231"/>
+      <c r="C1" s="231"/>
+      <c r="D1" s="231"/>
+      <c r="E1" s="231"/>
+      <c r="F1" s="231"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="222"/>
-      <c r="B2" s="222"/>
-      <c r="C2" s="222"/>
-      <c r="D2" s="222"/>
-      <c r="E2" s="222"/>
-      <c r="F2" s="222"/>
+      <c r="A2" s="231"/>
+      <c r="B2" s="231"/>
+      <c r="C2" s="231"/>
+      <c r="D2" s="231"/>
+      <c r="E2" s="231"/>
+      <c r="F2" s="231"/>
     </row>
     <row r="3" spans="1:15" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="84" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B3" s="85"/>
       <c r="C3" s="85"/>
@@ -8015,31 +8003,31 @@
     <row r="4" spans="1:15" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="87"/>
       <c r="B4" s="87" t="s">
+        <v>156</v>
+      </c>
+      <c r="C4" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="52" t="s">
+        <v>158</v>
+      </c>
+      <c r="E4" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="F4" s="53" t="s">
+        <v>160</v>
+      </c>
+      <c r="G4" s="87" t="s">
+        <v>161</v>
+      </c>
+      <c r="H4" s="232" t="s">
         <v>162</v>
       </c>
-      <c r="C4" s="51" t="s">
-        <v>163</v>
-      </c>
-      <c r="D4" s="52" t="s">
-        <v>164</v>
-      </c>
-      <c r="E4" s="52" t="s">
-        <v>165</v>
-      </c>
-      <c r="F4" s="53" t="s">
-        <v>166</v>
-      </c>
-      <c r="G4" s="87" t="s">
-        <v>167</v>
-      </c>
-      <c r="H4" s="223" t="s">
-        <v>168</v>
-      </c>
-      <c r="I4" s="224"/>
+      <c r="I4" s="233"/>
     </row>
     <row r="5" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="88" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B5" s="88">
         <v>300</v>
@@ -8062,12 +8050,12 @@
         <f>F5/B5</f>
         <v>0.17666666666666667</v>
       </c>
-      <c r="H5" s="225"/>
-      <c r="I5" s="226"/>
+      <c r="H5" s="234"/>
+      <c r="I5" s="235"/>
     </row>
     <row r="6" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="93" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B6" s="93">
         <v>100</v>
@@ -8089,12 +8077,12 @@
         <f>F6/B6</f>
         <v>0.05</v>
       </c>
-      <c r="H6" s="225"/>
-      <c r="I6" s="226"/>
+      <c r="H6" s="234"/>
+      <c r="I6" s="235"/>
     </row>
     <row r="7" spans="1:15" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="97" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B7" s="97">
         <v>100</v>
@@ -8116,52 +8104,52 @@
         <f>F7/B7</f>
         <v>0.05</v>
       </c>
-      <c r="H7" s="227"/>
-      <c r="I7" s="228"/>
+      <c r="H7" s="236"/>
+      <c r="I7" s="237"/>
     </row>
     <row r="8" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="9" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="102"/>
       <c r="B9" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" s="104" t="s">
+        <v>167</v>
+      </c>
+      <c r="D9" s="105" t="s">
+        <v>168</v>
+      </c>
+      <c r="E9" s="106" t="s">
+        <v>169</v>
+      </c>
+      <c r="F9" s="107" t="s">
+        <v>170</v>
+      </c>
+      <c r="G9" s="108" t="s">
+        <v>171</v>
+      </c>
+      <c r="H9" s="109" t="s">
         <v>172</v>
       </c>
-      <c r="C9" s="104" t="s">
+      <c r="I9" s="110" t="s">
         <v>173</v>
       </c>
-      <c r="D9" s="105" t="s">
+      <c r="J9" s="111" t="s">
+        <v>171</v>
+      </c>
+      <c r="K9" s="112" t="s">
         <v>174</v>
       </c>
-      <c r="E9" s="106" t="s">
+      <c r="L9" s="113" t="s">
         <v>175</v>
       </c>
-      <c r="F9" s="107" t="s">
-        <v>176</v>
-      </c>
-      <c r="G9" s="108" t="s">
-        <v>177</v>
-      </c>
-      <c r="H9" s="109" t="s">
-        <v>178</v>
-      </c>
-      <c r="I9" s="110" t="s">
-        <v>179</v>
-      </c>
-      <c r="J9" s="111" t="s">
-        <v>177</v>
-      </c>
-      <c r="K9" s="112" t="s">
-        <v>180</v>
-      </c>
-      <c r="L9" s="113" t="s">
-        <v>181</v>
-      </c>
       <c r="M9" s="113" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="114" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B10" s="115">
         <v>300</v>
@@ -8205,7 +8193,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="127" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B11" s="128">
         <v>100</v>
@@ -8251,7 +8239,7 @@
     </row>
     <row r="12" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="137" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B12" s="138">
         <v>100</v>
@@ -8311,102 +8299,102 @@
       <c r="M13" s="150"/>
     </row>
     <row r="14" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="229" t="s">
-        <v>182</v>
-      </c>
-      <c r="B14" s="230"/>
-      <c r="C14" s="230"/>
-      <c r="D14" s="230"/>
-      <c r="E14" s="231" t="s">
-        <v>183</v>
-      </c>
-      <c r="F14" s="231"/>
-      <c r="G14" s="231"/>
-      <c r="H14" s="231"/>
+      <c r="A14" s="238" t="s">
+        <v>176</v>
+      </c>
+      <c r="B14" s="239"/>
+      <c r="C14" s="239"/>
+      <c r="D14" s="239"/>
+      <c r="E14" s="240" t="s">
+        <v>177</v>
+      </c>
+      <c r="F14" s="240"/>
+      <c r="G14" s="240"/>
+      <c r="H14" s="240"/>
       <c r="I14" s="151"/>
-      <c r="J14" s="232" t="s">
-        <v>184</v>
-      </c>
-      <c r="K14" s="233"/>
-      <c r="L14" s="233"/>
-      <c r="M14" s="234"/>
+      <c r="J14" s="217" t="s">
+        <v>178</v>
+      </c>
+      <c r="K14" s="218"/>
+      <c r="L14" s="218"/>
+      <c r="M14" s="219"/>
       <c r="N14" s="152"/>
       <c r="O14" s="152"/>
     </row>
     <row r="15" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="230"/>
-      <c r="B15" s="230"/>
-      <c r="C15" s="230"/>
-      <c r="D15" s="230"/>
-      <c r="E15" s="231"/>
-      <c r="F15" s="231"/>
-      <c r="G15" s="231"/>
-      <c r="H15" s="231"/>
+      <c r="A15" s="239"/>
+      <c r="B15" s="239"/>
+      <c r="C15" s="239"/>
+      <c r="D15" s="239"/>
+      <c r="E15" s="240"/>
+      <c r="F15" s="240"/>
+      <c r="G15" s="240"/>
+      <c r="H15" s="240"/>
       <c r="I15" s="151"/>
-      <c r="J15" s="235"/>
-      <c r="K15" s="236"/>
-      <c r="L15" s="236"/>
-      <c r="M15" s="237"/>
+      <c r="J15" s="220"/>
+      <c r="K15" s="221"/>
+      <c r="L15" s="221"/>
+      <c r="M15" s="222"/>
       <c r="N15" s="152"/>
       <c r="O15" s="152"/>
     </row>
     <row r="16" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="230"/>
-      <c r="B16" s="230"/>
-      <c r="C16" s="230"/>
-      <c r="D16" s="230"/>
-      <c r="E16" s="231"/>
-      <c r="F16" s="231"/>
-      <c r="G16" s="231"/>
-      <c r="H16" s="231"/>
+      <c r="A16" s="239"/>
+      <c r="B16" s="239"/>
+      <c r="C16" s="239"/>
+      <c r="D16" s="239"/>
+      <c r="E16" s="240"/>
+      <c r="F16" s="240"/>
+      <c r="G16" s="240"/>
+      <c r="H16" s="240"/>
       <c r="I16" s="151"/>
-      <c r="J16" s="235"/>
-      <c r="K16" s="236"/>
-      <c r="L16" s="236"/>
-      <c r="M16" s="237"/>
+      <c r="J16" s="220"/>
+      <c r="K16" s="221"/>
+      <c r="L16" s="221"/>
+      <c r="M16" s="222"/>
       <c r="N16" s="152"/>
       <c r="O16" s="152"/>
     </row>
     <row r="17" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="230"/>
-      <c r="B17" s="230"/>
-      <c r="C17" s="230"/>
-      <c r="D17" s="230"/>
-      <c r="E17" s="231"/>
-      <c r="F17" s="231"/>
-      <c r="G17" s="231"/>
-      <c r="H17" s="231"/>
+      <c r="A17" s="239"/>
+      <c r="B17" s="239"/>
+      <c r="C17" s="239"/>
+      <c r="D17" s="239"/>
+      <c r="E17" s="240"/>
+      <c r="F17" s="240"/>
+      <c r="G17" s="240"/>
+      <c r="H17" s="240"/>
       <c r="I17" s="151"/>
-      <c r="J17" s="235"/>
-      <c r="K17" s="236"/>
-      <c r="L17" s="236"/>
-      <c r="M17" s="237"/>
+      <c r="J17" s="220"/>
+      <c r="K17" s="221"/>
+      <c r="L17" s="221"/>
+      <c r="M17" s="222"/>
       <c r="N17" s="152"/>
       <c r="O17" s="152"/>
     </row>
     <row r="18" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H18" s="150"/>
-      <c r="J18" s="238"/>
-      <c r="K18" s="239"/>
-      <c r="L18" s="239"/>
-      <c r="M18" s="240"/>
+      <c r="J18" s="223"/>
+      <c r="K18" s="224"/>
+      <c r="L18" s="224"/>
+      <c r="M18" s="225"/>
       <c r="N18" s="152"/>
       <c r="O18" s="152"/>
     </row>
     <row r="19" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="153" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B19" s="154" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C19" s="155" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="156" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B20" s="157">
         <v>8</v>
@@ -8417,7 +8405,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="159" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B21" s="13">
         <v>2</v>
@@ -8428,7 +8416,7 @@
     </row>
     <row r="22" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="161" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B22" s="3">
         <v>2</v>
@@ -8440,40 +8428,40 @@
     <row r="23" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="24" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="162" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B24" s="163" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C24" s="163" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D24" s="164" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E24" s="162" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F24" s="163" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G24" s="163" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H24" s="164" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I24" s="162" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="J24" s="163" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K24" s="163" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L24" s="164" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -9037,11 +9025,11 @@
         <v>292300</v>
       </c>
       <c r="H40" s="168"/>
-      <c r="I40" s="217" t="s">
-        <v>188</v>
-      </c>
-      <c r="J40" s="218"/>
-      <c r="K40" s="218"/>
+      <c r="I40" s="226" t="s">
+        <v>182</v>
+      </c>
+      <c r="J40" s="227"/>
+      <c r="K40" s="227"/>
       <c r="L40" s="172">
         <f>SUM(L25:L39)</f>
         <v>2</v>
@@ -9085,11 +9073,11 @@
         <v>255800</v>
       </c>
       <c r="D42" s="168"/>
-      <c r="E42" s="217" t="s">
-        <v>188</v>
-      </c>
-      <c r="F42" s="218"/>
-      <c r="G42" s="218"/>
+      <c r="E42" s="226" t="s">
+        <v>182</v>
+      </c>
+      <c r="F42" s="227"/>
+      <c r="G42" s="227"/>
       <c r="H42" s="172">
         <f>SUM(H25:H41)</f>
         <v>2</v>
@@ -9137,11 +9125,11 @@
       </c>
     </row>
     <row r="46" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="219" t="s">
-        <v>188</v>
-      </c>
-      <c r="B46" s="220"/>
-      <c r="C46" s="220"/>
+      <c r="A46" s="228" t="s">
+        <v>182</v>
+      </c>
+      <c r="B46" s="229"/>
+      <c r="C46" s="229"/>
       <c r="D46" s="173">
         <f>SUM(D25:D45)</f>
         <v>8</v>
@@ -9191,22 +9179,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="221" t="s">
-        <v>160</v>
-      </c>
-      <c r="B1" s="222"/>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
-      <c r="F1" s="222"/>
+      <c r="A1" s="230" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="231"/>
+      <c r="C1" s="231"/>
+      <c r="D1" s="231"/>
+      <c r="E1" s="231"/>
+      <c r="F1" s="231"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="222"/>
-      <c r="B2" s="222"/>
-      <c r="C2" s="222"/>
-      <c r="D2" s="222"/>
-      <c r="E2" s="222"/>
-      <c r="F2" s="222"/>
+      <c r="A2" s="231"/>
+      <c r="B2" s="231"/>
+      <c r="C2" s="231"/>
+      <c r="D2" s="231"/>
+      <c r="E2" s="231"/>
+      <c r="F2" s="231"/>
     </row>
     <row r="3" spans="1:13" ht="26.25" x14ac:dyDescent="0.3">
       <c r="A3" s="175"/>
@@ -9218,51 +9206,51 @@
     </row>
     <row r="4" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="102"/>
       <c r="B5" s="103" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C5" s="104" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D5" s="105" t="s">
+        <v>168</v>
+      </c>
+      <c r="E5" s="176" t="s">
+        <v>184</v>
+      </c>
+      <c r="F5" s="177" t="s">
+        <v>185</v>
+      </c>
+      <c r="G5" s="108" t="s">
+        <v>171</v>
+      </c>
+      <c r="H5" s="178" t="s">
+        <v>186</v>
+      </c>
+      <c r="I5" s="179" t="s">
+        <v>187</v>
+      </c>
+      <c r="J5" s="111" t="s">
+        <v>171</v>
+      </c>
+      <c r="K5" s="112" t="s">
         <v>174</v>
       </c>
-      <c r="E5" s="176" t="s">
-        <v>190</v>
-      </c>
-      <c r="F5" s="177" t="s">
-        <v>191</v>
-      </c>
-      <c r="G5" s="108" t="s">
-        <v>177</v>
-      </c>
-      <c r="H5" s="178" t="s">
-        <v>192</v>
-      </c>
-      <c r="I5" s="179" t="s">
-        <v>193</v>
-      </c>
-      <c r="J5" s="111" t="s">
-        <v>177</v>
-      </c>
-      <c r="K5" s="112" t="s">
-        <v>180</v>
-      </c>
       <c r="L5" s="113" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="M5" s="113" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="114" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B6" s="115">
         <v>300</v>
@@ -9306,7 +9294,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="127" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B7" s="128">
         <v>100</v>
@@ -9352,7 +9340,7 @@
     </row>
     <row r="8" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="137" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B8" s="138">
         <v>100</v>
@@ -9412,293 +9400,293 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="28" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="247" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="F11" s="13" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="268" t="s">
-        <v>195</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>200</v>
-      </c>
       <c r="G11" s="13" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="262"/>
-      <c r="B12" s="264"/>
-      <c r="C12" s="264"/>
-      <c r="D12" s="266"/>
+      <c r="A12" s="241"/>
+      <c r="B12" s="243"/>
+      <c r="C12" s="243"/>
+      <c r="D12" s="245"/>
       <c r="E12" s="180"/>
       <c r="F12" s="180"/>
       <c r="G12" s="180"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="263"/>
-      <c r="B13" s="265"/>
-      <c r="C13" s="265"/>
-      <c r="D13" s="267"/>
+      <c r="A13" s="242"/>
+      <c r="B13" s="244"/>
+      <c r="C13" s="244"/>
+      <c r="D13" s="246"/>
       <c r="E13" s="181"/>
       <c r="F13" s="181"/>
       <c r="G13" s="181"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="262" t="s">
-        <v>201</v>
-      </c>
-      <c r="B14" s="264"/>
-      <c r="C14" s="264"/>
-      <c r="D14" s="266"/>
+      <c r="A14" s="241" t="s">
+        <v>195</v>
+      </c>
+      <c r="B14" s="243"/>
+      <c r="C14" s="243"/>
+      <c r="D14" s="245"/>
       <c r="E14" s="180"/>
       <c r="F14" s="180"/>
       <c r="G14" s="180"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="263"/>
-      <c r="B15" s="265"/>
-      <c r="C15" s="265"/>
-      <c r="D15" s="267"/>
+      <c r="A15" s="242"/>
+      <c r="B15" s="244"/>
+      <c r="C15" s="244"/>
+      <c r="D15" s="246"/>
       <c r="E15" s="181"/>
       <c r="F15" s="181"/>
       <c r="G15" s="181"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="262" t="s">
-        <v>202</v>
-      </c>
-      <c r="B16" s="264"/>
-      <c r="C16" s="264"/>
-      <c r="D16" s="266"/>
+      <c r="A16" s="241" t="s">
+        <v>196</v>
+      </c>
+      <c r="B16" s="243"/>
+      <c r="C16" s="243"/>
+      <c r="D16" s="245"/>
       <c r="E16" s="180"/>
       <c r="F16" s="180"/>
       <c r="G16" s="180"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="263"/>
-      <c r="B17" s="265"/>
-      <c r="C17" s="265"/>
-      <c r="D17" s="267"/>
+      <c r="A17" s="242"/>
+      <c r="B17" s="244"/>
+      <c r="C17" s="244"/>
+      <c r="D17" s="246"/>
       <c r="E17" s="181"/>
       <c r="F17" s="181"/>
       <c r="G17" s="181"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="250" t="s">
-        <v>203</v>
-      </c>
-      <c r="B20" s="250"/>
+      <c r="A20" s="248" t="s">
+        <v>197</v>
+      </c>
+      <c r="B20" s="248"/>
       <c r="D20" s="200" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E20" s="200"/>
       <c r="G20" s="200" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="H20" s="200"/>
     </row>
     <row r="21" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="250"/>
-      <c r="B21" s="250"/>
+      <c r="A21" s="248"/>
+      <c r="B21" s="248"/>
       <c r="C21" s="13" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E21" s="13"/>
       <c r="G21" s="200" t="s">
-        <v>208</v>
-      </c>
-      <c r="H21" s="252"/>
-      <c r="I21" s="253" t="s">
-        <v>209</v>
-      </c>
-      <c r="J21" s="254"/>
-      <c r="K21" s="254"/>
-      <c r="L21" s="254"/>
-      <c r="M21" s="255"/>
+        <v>202</v>
+      </c>
+      <c r="H21" s="249"/>
+      <c r="I21" s="250" t="s">
+        <v>203</v>
+      </c>
+      <c r="J21" s="251"/>
+      <c r="K21" s="251"/>
+      <c r="L21" s="251"/>
+      <c r="M21" s="252"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="250"/>
-      <c r="B22" s="250"/>
+      <c r="A22" s="248"/>
+      <c r="B22" s="248"/>
       <c r="C22" s="13" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="E22" s="13"/>
       <c r="G22" s="200"/>
-      <c r="H22" s="252"/>
-      <c r="I22" s="256"/>
-      <c r="J22" s="257"/>
-      <c r="K22" s="257"/>
-      <c r="L22" s="257"/>
-      <c r="M22" s="258"/>
+      <c r="H22" s="249"/>
+      <c r="I22" s="253"/>
+      <c r="J22" s="254"/>
+      <c r="K22" s="254"/>
+      <c r="L22" s="254"/>
+      <c r="M22" s="255"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="250"/>
-      <c r="B23" s="250"/>
+      <c r="A23" s="248"/>
+      <c r="B23" s="248"/>
       <c r="C23" s="13" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E23" s="13"/>
       <c r="G23" s="200"/>
-      <c r="H23" s="252"/>
-      <c r="I23" s="256"/>
-      <c r="J23" s="257"/>
-      <c r="K23" s="257"/>
-      <c r="L23" s="257"/>
-      <c r="M23" s="258"/>
+      <c r="H23" s="249"/>
+      <c r="I23" s="253"/>
+      <c r="J23" s="254"/>
+      <c r="K23" s="254"/>
+      <c r="L23" s="254"/>
+      <c r="M23" s="255"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="250"/>
-      <c r="B24" s="250"/>
+      <c r="A24" s="248"/>
+      <c r="B24" s="248"/>
       <c r="C24" s="13" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="E24" s="13"/>
       <c r="G24" s="200"/>
-      <c r="H24" s="252"/>
-      <c r="I24" s="256"/>
-      <c r="J24" s="257"/>
-      <c r="K24" s="257"/>
-      <c r="L24" s="257"/>
-      <c r="M24" s="258"/>
+      <c r="H24" s="249"/>
+      <c r="I24" s="253"/>
+      <c r="J24" s="254"/>
+      <c r="K24" s="254"/>
+      <c r="L24" s="254"/>
+      <c r="M24" s="255"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D25" s="13" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E25" s="48"/>
       <c r="G25" s="200"/>
-      <c r="H25" s="252"/>
-      <c r="I25" s="259"/>
-      <c r="J25" s="260"/>
-      <c r="K25" s="260"/>
-      <c r="L25" s="260"/>
-      <c r="M25" s="261"/>
+      <c r="H25" s="249"/>
+      <c r="I25" s="256"/>
+      <c r="J25" s="257"/>
+      <c r="K25" s="257"/>
+      <c r="L25" s="257"/>
+      <c r="M25" s="258"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" s="241" t="s">
-        <v>217</v>
-      </c>
-      <c r="B27" s="241"/>
+      <c r="A27" s="259" t="s">
+        <v>211</v>
+      </c>
+      <c r="B27" s="259"/>
       <c r="D27" s="200" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E27" s="200"/>
       <c r="G27" s="200" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="H27" s="200"/>
-      <c r="I27" s="253" t="s">
-        <v>218</v>
-      </c>
-      <c r="J27" s="254"/>
-      <c r="K27" s="255"/>
+      <c r="I27" s="250" t="s">
+        <v>212</v>
+      </c>
+      <c r="J27" s="251"/>
+      <c r="K27" s="252"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" s="241"/>
-      <c r="B28" s="241"/>
+      <c r="A28" s="259"/>
+      <c r="B28" s="259"/>
       <c r="C28" s="13" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E28" s="13"/>
       <c r="G28" s="200" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="H28" s="200"/>
-      <c r="I28" s="256"/>
-      <c r="J28" s="257"/>
-      <c r="K28" s="258"/>
+      <c r="I28" s="253"/>
+      <c r="J28" s="254"/>
+      <c r="K28" s="255"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A29" s="241"/>
-      <c r="B29" s="241"/>
+      <c r="A29" s="259"/>
+      <c r="B29" s="259"/>
       <c r="C29" s="13" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E29" s="13"/>
       <c r="G29" s="200"/>
       <c r="H29" s="200"/>
-      <c r="I29" s="256"/>
-      <c r="J29" s="257"/>
-      <c r="K29" s="258"/>
+      <c r="I29" s="253"/>
+      <c r="J29" s="254"/>
+      <c r="K29" s="255"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A30" s="241"/>
-      <c r="B30" s="241"/>
+      <c r="A30" s="259"/>
+      <c r="B30" s="259"/>
       <c r="C30" s="13" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="E30" s="13"/>
       <c r="G30" s="200"/>
       <c r="H30" s="200"/>
-      <c r="I30" s="256"/>
-      <c r="J30" s="257"/>
-      <c r="K30" s="258"/>
+      <c r="I30" s="253"/>
+      <c r="J30" s="254"/>
+      <c r="K30" s="255"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D31" s="13" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E31" s="13"/>
       <c r="G31" s="200"/>
       <c r="H31" s="200"/>
-      <c r="I31" s="259"/>
-      <c r="J31" s="260"/>
-      <c r="K31" s="261"/>
+      <c r="I31" s="256"/>
+      <c r="J31" s="257"/>
+      <c r="K31" s="258"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="250" t="s">
-        <v>222</v>
-      </c>
-      <c r="B36" s="250"/>
+      <c r="A36" s="248" t="s">
+        <v>216</v>
+      </c>
+      <c r="B36" s="248"/>
       <c r="D36" s="200" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E36" s="200"/>
       <c r="G36" s="200" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="H36" s="200"/>
-      <c r="I36" s="251" t="s">
-        <v>223</v>
+      <c r="I36" s="260" t="s">
+        <v>217</v>
       </c>
       <c r="J36" s="199"/>
       <c r="K36" s="199"/>
@@ -9706,84 +9694,84 @@
       <c r="M36" s="199"/>
     </row>
     <row r="37" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="250"/>
-      <c r="B37" s="250"/>
+      <c r="A37" s="248"/>
+      <c r="B37" s="248"/>
       <c r="C37" s="13" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E37" s="13">
         <v>6</v>
       </c>
       <c r="G37" s="200" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="H37" s="200">
         <v>100</v>
       </c>
-      <c r="I37" s="251"/>
+      <c r="I37" s="260"/>
       <c r="J37" s="199"/>
       <c r="K37" s="199"/>
       <c r="L37" s="199"/>
       <c r="M37" s="199"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" s="250"/>
-      <c r="B38" s="250"/>
+      <c r="A38" s="248"/>
+      <c r="B38" s="248"/>
       <c r="C38" s="13" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="E38" s="13">
         <v>2</v>
       </c>
       <c r="G38" s="200"/>
       <c r="H38" s="200"/>
-      <c r="I38" s="251"/>
+      <c r="I38" s="260"/>
       <c r="J38" s="199"/>
       <c r="K38" s="199"/>
       <c r="L38" s="199"/>
       <c r="M38" s="199"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A39" s="250"/>
-      <c r="B39" s="250"/>
+      <c r="A39" s="248"/>
+      <c r="B39" s="248"/>
       <c r="C39" s="13" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E39" s="13">
         <v>1</v>
       </c>
       <c r="G39" s="200"/>
       <c r="H39" s="200"/>
-      <c r="I39" s="251"/>
+      <c r="I39" s="260"/>
       <c r="J39" s="199"/>
       <c r="K39" s="199"/>
       <c r="L39" s="199"/>
       <c r="M39" s="199"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A40" s="250"/>
-      <c r="B40" s="250"/>
+      <c r="A40" s="248"/>
+      <c r="B40" s="248"/>
       <c r="C40" s="13" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="E40" s="13">
         <v>1</v>
       </c>
       <c r="G40" s="200"/>
       <c r="H40" s="200"/>
-      <c r="I40" s="251"/>
+      <c r="I40" s="260"/>
       <c r="J40" s="199"/>
       <c r="K40" s="199"/>
       <c r="L40" s="199"/>
@@ -9791,7 +9779,7 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D41" s="13" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E41" s="48">
         <f>SUM(E37:E40)</f>
@@ -9799,92 +9787,92 @@
       </c>
       <c r="G41" s="200"/>
       <c r="H41" s="200"/>
-      <c r="I41" s="251"/>
+      <c r="I41" s="260"/>
       <c r="J41" s="199"/>
       <c r="K41" s="199"/>
       <c r="L41" s="199"/>
       <c r="M41" s="199"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="241" t="s">
-        <v>224</v>
-      </c>
-      <c r="B43" s="241"/>
+      <c r="A43" s="259" t="s">
+        <v>218</v>
+      </c>
+      <c r="B43" s="259"/>
       <c r="D43" s="200" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E43" s="200"/>
       <c r="G43" s="200" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="H43" s="200"/>
-      <c r="I43" s="242" t="s">
-        <v>225</v>
-      </c>
-      <c r="J43" s="243"/>
-      <c r="K43" s="244"/>
+      <c r="I43" s="261" t="s">
+        <v>219</v>
+      </c>
+      <c r="J43" s="262"/>
+      <c r="K43" s="263"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="241"/>
-      <c r="B44" s="241"/>
+      <c r="A44" s="259"/>
+      <c r="B44" s="259"/>
       <c r="C44" s="13" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E44" s="13">
         <v>8</v>
       </c>
       <c r="G44" s="200" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="H44" s="200">
         <v>100</v>
       </c>
-      <c r="I44" s="245"/>
-      <c r="J44" s="188"/>
-      <c r="K44" s="246"/>
+      <c r="I44" s="264"/>
+      <c r="J44" s="182"/>
+      <c r="K44" s="265"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" s="241"/>
-      <c r="B45" s="241"/>
+      <c r="A45" s="259"/>
+      <c r="B45" s="259"/>
       <c r="C45" s="13" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E45" s="13">
         <v>2</v>
       </c>
       <c r="G45" s="200"/>
       <c r="H45" s="200"/>
-      <c r="I45" s="245"/>
-      <c r="J45" s="188"/>
-      <c r="K45" s="246"/>
+      <c r="I45" s="264"/>
+      <c r="J45" s="182"/>
+      <c r="K45" s="265"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="241"/>
-      <c r="B46" s="241"/>
+      <c r="A46" s="259"/>
+      <c r="B46" s="259"/>
       <c r="C46" s="13" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="E46" s="13">
         <v>1</v>
       </c>
       <c r="G46" s="200"/>
       <c r="H46" s="200"/>
-      <c r="I46" s="245"/>
-      <c r="J46" s="188"/>
-      <c r="K46" s="246"/>
+      <c r="I46" s="264"/>
+      <c r="J46" s="182"/>
+      <c r="K46" s="265"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D47" s="13" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E47" s="13">
         <f>SUM(E44:E46)</f>
@@ -9892,27 +9880,24 @@
       </c>
       <c r="G47" s="200"/>
       <c r="H47" s="200"/>
-      <c r="I47" s="247"/>
-      <c r="J47" s="248"/>
-      <c r="K47" s="249"/>
+      <c r="I47" s="266"/>
+      <c r="J47" s="267"/>
+      <c r="K47" s="268"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="A1:F2"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="A20:B24"/>
-    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A43:B46"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:K47"/>
+    <mergeCell ref="G44:G47"/>
+    <mergeCell ref="H44:H47"/>
+    <mergeCell ref="A36:B40"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:M41"/>
+    <mergeCell ref="G37:G41"/>
+    <mergeCell ref="H37:H41"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="G21:G25"/>
     <mergeCell ref="H21:H25"/>
@@ -9923,18 +9908,21 @@
     <mergeCell ref="I27:K31"/>
     <mergeCell ref="G28:G31"/>
     <mergeCell ref="H28:H31"/>
-    <mergeCell ref="A36:B40"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I36:M41"/>
-    <mergeCell ref="G37:G41"/>
-    <mergeCell ref="H37:H41"/>
-    <mergeCell ref="A43:B46"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="I43:K47"/>
-    <mergeCell ref="G44:G47"/>
-    <mergeCell ref="H44:H47"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="A20:B24"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
